--- a/p6_deployment/data/germany/missing/data_understanding/all/df_match_miss.xlsx
+++ b/p6_deployment/data/germany/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD42"/>
+  <dimension ref="A1:BF43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,6 +704,16 @@
           <t>red_cards_away</t>
         </is>
       </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -730,7 +740,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>54 600</t>
+          <t>47 000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -941,7 +951,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>AoL97rX</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -951,7 +961,7 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>xzRzG0V</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -975,6 +985,8 @@
       </c>
       <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1211,7 +1223,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>xzRzG0V</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1221,7 +1233,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>AoL97rX</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1245,6 +1257,8 @@
       </c>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1481,7 +1495,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>hAcTWKK</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1491,7 +1505,7 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2VSFgl3</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1515,6 +1529,8 @@
       </c>
       <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1541,14 +1557,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>62 000</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>81 365</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>81 365</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>4</t>
@@ -1751,7 +1767,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>Q1njn0V</t>
+          <t>Q1njn0Vm</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1761,7 +1777,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>MDhPV0R</t>
+          <t>MDhPV0RQ</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1785,6 +1801,8 @@
       </c>
       <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1811,7 +1829,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>58 000</t>
+          <t>47 000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2021,7 +2039,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>UgdQz0f</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2031,7 +2049,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>pfoInmc</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2055,6 +2073,8 @@
       </c>
       <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -2291,7 +2311,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>8W0vrAR</t>
+          <t>8W0vrAR9</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2301,7 +2321,7 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lGJdeem</t>
+          <t>lGJdeemM</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -2325,6 +2345,8 @@
       </c>
       <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2561,7 +2583,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>KUx4Q7x</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2571,7 +2593,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>CQTUFgP</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2595,6 +2617,8 @@
       </c>
       <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -2621,7 +2645,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>60 449</t>
+          <t>54 800</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2831,7 +2855,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>GzfvcwR</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2841,7 +2865,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>M5BRZDs</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -2865,6 +2889,8 @@
       </c>
       <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -3101,7 +3127,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>v9WoiHG</t>
+          <t>v9WoiHGP</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -3111,7 +3137,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>l0fHXMd</t>
+          <t>l0fHXMdE</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3135,6 +3161,8 @@
       </c>
       <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -3371,7 +3399,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>4fuCGs9</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -3381,7 +3409,7 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>xzRzG0V</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -3405,6 +3433,8 @@
       </c>
       <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -3641,7 +3671,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>f3ddUIX</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -3651,7 +3681,7 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>vZA6VYp</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -3675,6 +3705,8 @@
       </c>
       <c r="BC12" t="inlineStr"/>
       <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -3911,7 +3943,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>xzRzG0V</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -3921,7 +3953,7 @@
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>hAcTWKK</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -3953,6 +3985,8 @@
           <t>0</t>
         </is>
       </c>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -3979,7 +4013,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75 024</t>
+          <t>66 000</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4189,7 +4223,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>CQTUFgP</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -4199,7 +4233,7 @@
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>f3ddUIX</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -4223,6 +4257,8 @@
       </c>
       <c r="BC14" t="inlineStr"/>
       <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -4459,7 +4495,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>MDhPV0R</t>
+          <t>MDhPV0RQ</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -4469,7 +4505,7 @@
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>KUx4Q7x</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -4493,6 +4529,8 @@
       </c>
       <c r="BC15" t="inlineStr"/>
       <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -4729,7 +4767,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>vZA6VYp</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -4739,7 +4777,7 @@
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Q1njn0V</t>
+          <t>Q1njn0Vm</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -4763,6 +4801,8 @@
       </c>
       <c r="BC16" t="inlineStr"/>
       <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -4999,7 +5039,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>M5BRZDs</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -5009,7 +5049,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>UgdQz0f</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -5033,6 +5073,8 @@
       </c>
       <c r="BC17" t="inlineStr"/>
       <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -5059,14 +5101,14 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>43 000</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>50 000</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>50 000</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>3</t>
@@ -5269,7 +5311,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>lGJdeem</t>
+          <t>lGJdeemM</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -5279,7 +5321,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>v9WoiHG</t>
+          <t>v9WoiHGP</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -5303,6 +5345,8 @@
       </c>
       <c r="BC18" t="inlineStr"/>
       <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -5539,7 +5583,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>l0fHXMd</t>
+          <t>l0fHXMdE</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -5549,7 +5593,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>4ljanuk</t>
+          <t>4ljanukM</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -5573,6 +5617,8 @@
       </c>
       <c r="BC19" t="inlineStr"/>
       <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -5599,14 +5645,14 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>40 000</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>47 069</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>47 069</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>1</t>
@@ -5809,7 +5855,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>pfoInmc</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -5819,7 +5865,7 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>4fuCGs9</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -5843,6 +5889,8 @@
       </c>
       <c r="BC20" t="inlineStr"/>
       <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -6079,7 +6127,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2VSFgl3</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -6089,7 +6137,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>GzfvcwR</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -6113,6 +6161,8 @@
       </c>
       <c r="BC21" t="inlineStr"/>
       <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -6350,7 +6400,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>QTAUlvU</t>
+          <t>QTAUlvUP</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -6360,7 +6410,7 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>zyLSrbZ</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -6384,6 +6434,8 @@
       </c>
       <c r="BC22" t="inlineStr"/>
       <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -6620,7 +6672,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>zyLSrbZ</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -6630,7 +6682,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>WvI4Hnn</t>
+          <t>WvI4Hnn1</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -6654,6 +6706,8 @@
       </c>
       <c r="BC23" t="inlineStr"/>
       <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -6680,7 +6734,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>54 600</t>
+          <t>47 000</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -6890,7 +6944,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>AoL97rX</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -6900,7 +6954,7 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>IgZoGKF</t>
+          <t>IgZoGKFn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -6932,6 +6986,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -7168,7 +7224,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>8E8qmw3</t>
+          <t>8E8qmw3d</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -7178,7 +7234,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>OzPMRhK</t>
+          <t>OzPMRhK3</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -7202,6 +7258,8 @@
       </c>
       <c r="BC25" t="inlineStr"/>
       <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -7438,7 +7496,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>8E86CPu</t>
+          <t>8E86CPuD</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -7448,7 +7506,7 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>txZLBQV</t>
+          <t>txZLBQVC</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -7472,6 +7530,8 @@
       </c>
       <c r="BC26" t="inlineStr"/>
       <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -7498,7 +7558,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>57 274</t>
+          <t>49 000</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -7708,7 +7768,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>EDRZkDz</t>
+          <t>EDRZkDzS</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -7718,7 +7778,7 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>YmfcAeC</t>
+          <t>YmfcAeCo</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -7742,6 +7802,8 @@
       </c>
       <c r="BC27" t="inlineStr"/>
       <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -7978,7 +8040,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>t0ZPdkU</t>
+          <t>t0ZPdkUl</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -7988,7 +8050,7 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>A15eUM4</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -8012,6 +8074,8 @@
       </c>
       <c r="BC28" t="inlineStr"/>
       <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -8248,7 +8312,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>UyNNTYW</t>
+          <t>UyNNTYWE</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -8258,7 +8322,7 @@
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>0AI1QUJ</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -8282,6 +8346,8 @@
       </c>
       <c r="BC29" t="inlineStr"/>
       <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -8518,7 +8584,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2BYSk4K</t>
+          <t>2BYSk4KO</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -8528,7 +8594,7 @@
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>SQrxFAM</t>
+          <t>SQrxFAMl</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -8560,6 +8626,8 @@
           <t>0</t>
         </is>
       </c>
+      <c r="BE30" t="inlineStr"/>
+      <c r="BF30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -8796,7 +8864,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>lxrr7Dg</t>
+          <t>lxrr7DgN</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -8806,7 +8874,7 @@
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>v12aAJd</t>
+          <t>v12aAJdR</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
@@ -8830,6 +8898,8 @@
       </c>
       <c r="BC31" t="inlineStr"/>
       <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr"/>
+      <c r="BF31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -9066,7 +9136,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>QTAUlvU</t>
+          <t>QTAUlvUP</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -9076,7 +9146,7 @@
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>QHesBmS</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -9100,6 +9170,8 @@
       </c>
       <c r="BC32" t="inlineStr"/>
       <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="inlineStr"/>
+      <c r="BF32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -9336,7 +9408,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>SQrxFAM</t>
+          <t>SQrxFAMl</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -9346,7 +9418,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>QTAUlvU</t>
+          <t>QTAUlvUP</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -9370,6 +9442,8 @@
       </c>
       <c r="BC33" t="inlineStr"/>
       <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="inlineStr"/>
+      <c r="BF33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -9606,7 +9680,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>OzPMRhK</t>
+          <t>OzPMRhK3</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -9616,7 +9690,7 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>t0ZPdkU</t>
+          <t>t0ZPdkUl</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
@@ -9640,6 +9714,8 @@
       </c>
       <c r="BC34" t="inlineStr"/>
       <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -9876,7 +9952,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>QHesBmS</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -9886,7 +9962,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>lxrr7Dg</t>
+          <t>lxrr7DgN</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -9910,6 +9986,8 @@
       </c>
       <c r="BC35" t="inlineStr"/>
       <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -10146,7 +10224,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>A15eUM4</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -10156,7 +10234,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>AoL97rX</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -10180,6 +10258,8 @@
       </c>
       <c r="BC36" t="inlineStr"/>
       <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr"/>
+      <c r="BF36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -10206,7 +10286,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>74 667</t>
+          <t>71 000</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -10416,7 +10496,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>v12aAJd</t>
+          <t>v12aAJdR</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -10426,7 +10506,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>2BYSk4K</t>
+          <t>2BYSk4KO</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -10450,6 +10530,8 @@
       </c>
       <c r="BC37" t="inlineStr"/>
       <c r="BD37" t="inlineStr"/>
+      <c r="BE37" t="inlineStr"/>
+      <c r="BF37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -10686,7 +10768,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>YmfcAeC</t>
+          <t>YmfcAeCo</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -10696,7 +10778,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>8E8qmw3</t>
+          <t>8E8qmw3d</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -10720,6 +10802,8 @@
       </c>
       <c r="BC38" t="inlineStr"/>
       <c r="BD38" t="inlineStr"/>
+      <c r="BE38" t="inlineStr"/>
+      <c r="BF38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -10746,7 +10830,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>62 271</t>
+          <t>50 000</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -10956,7 +11040,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>txZLBQV</t>
+          <t>txZLBQVC</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -10966,7 +11050,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>UyNNTYW</t>
+          <t>UyNNTYWE</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -10998,6 +11082,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -11234,7 +11320,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>IgZoGKF</t>
+          <t>IgZoGKFn</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -11244,7 +11330,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>8E86CPu</t>
+          <t>8E86CPuD</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -11268,6 +11354,8 @@
       </c>
       <c r="BC40" t="inlineStr"/>
       <c r="BD40" t="inlineStr"/>
+      <c r="BE40" t="inlineStr"/>
+      <c r="BF40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -11504,7 +11592,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>0AI1QUJ</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -11514,7 +11602,7 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>EDRZkDz</t>
+          <t>EDRZkDzS</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -11538,6 +11626,8 @@
       </c>
       <c r="BC41" t="inlineStr"/>
       <c r="BD41" t="inlineStr"/>
+      <c r="BE41" t="inlineStr"/>
+      <c r="BF41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -11770,7 +11860,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>lxrr7Dg</t>
+          <t>lxrr7DgN</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -11780,7 +11870,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>txZLBQV</t>
+          <t>txZLBQVC</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -11804,6 +11894,273 @@
       </c>
       <c r="BC42" t="inlineStr"/>
       <c r="BD42" t="inlineStr"/>
+      <c r="BE42" t="inlineStr"/>
+      <c r="BF42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>GfN42CgJ</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>25.05.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Dankert B.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Olympiastadion
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>71 000</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>74 322</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Kaiserslautern</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen
+Winner</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>2BYSk4KO</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>funkel friedhelm</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>alonso xabi</t>
+        </is>
+      </c>
+      <c r="AY43" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>2023_2024</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
